--- a/etf_holdings/2026-10-29_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-29_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:44</t>
+          <t>2026-10-29 23:19:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.04%2425</t>
+          <t>-0.41%2415</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2425</v>
+        <v>2415</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.93%753,000</t>
+          <t>9.63%753,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.93%</t>
+          <t>9.63%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:44</t>
+          <t>2026-10-29 23:19:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+6.94%4235</t>
+          <t>-4.49%4045</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+6.94%</t>
+          <t>-4.49%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4235</v>
+        <v>4045</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.42%249,000</t>
+          <t>5.56%249,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.42%</t>
+          <t>5.56%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:44</t>
+          <t>2026-10-29 23:19:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+3.47%10150</t>
+          <t>-2.66%9880</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+3.47%</t>
+          <t>-2.66%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>10150</v>
+        <v>9880</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.26%79,000</t>
+          <t>4.23%79,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>4.23%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:44</t>
+          <t>2026-10-29 23:19:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+5.79%5025</t>
+          <t>-0.3%5010</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+5.79%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5025</v>
+        <v>5010</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.76%144,000</t>
+          <t>3.82%144,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>3.82%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:44</t>
+          <t>2026-10-29 23:19:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+3.77%1100</t>
+          <t>-5.45%1040</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+3.77%</t>
+          <t>-5.45%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1100</v>
+        <v>1040</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.64%625,000</t>
+          <t>3.63%625,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.64%</t>
+          <t>3.63%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:44</t>
+          <t>2026-10-29 23:19:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+7.23%319</t>
+          <t>-2.19%312</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+7.23%</t>
+          <t>-2.19%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.46%2,117,000</t>
+          <t>3.56%2,117,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.56%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:44</t>
+          <t>2026-10-29 23:19:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+2.65%1550</t>
+          <t>-4.52%1480</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>-4.52%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1550</v>
+        <v>1480</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.35%404,000</t>
+          <t>3.30%404,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.30%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:44</t>
+          <t>2026-10-29 23:19:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+1.62%251.5</t>
+          <t>-1.39%248</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+1.62%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>251.5</v>
+        <v>248</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.33%2,453,000</t>
+          <t>3.25%2,453,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.25%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:44</t>
+          <t>2026-10-29 23:19:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+8.79%6375</t>
+          <t>+0.47%6405</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+8.79%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6375</v>
+        <v>6405</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.90%90,000</t>
+          <t>3.03%90,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>3.03%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:44</t>
+          <t>2026-10-29 23:19:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,12 +1058,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+8.16%477</t>
+          <t>0%477</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+8.16%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.34%967,000</t>
+          <t>2.43%967,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.43%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:44</t>
+          <t>2026-10-29 23:19:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+2.72%3215</t>
+          <t>-1.73%683</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+2.72%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3215</v>
+        <v>683</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.30%134,000</t>
+          <t>2.28%621,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>134000</v>
+        <v>621000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:44</t>
+          <t>2026-10-29 23:19:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+6.76%695</t>
+          <t>-3.42%3105</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+6.76%</t>
+          <t>-3.42%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>695</v>
+        <v>3105</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.22%621,000</t>
+          <t>2.27%134,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>621000</v>
+        <v>134000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:44</t>
+          <t>2026-10-29 23:19:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+5.58%6335</t>
+          <t>-8.21%5815</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+5.58%</t>
+          <t>-8.21%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6335</v>
+        <v>5815</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.14%65,000</t>
+          <t>2.17%65,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:44</t>
+          <t>2026-10-29 23:19:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+6.81%5565</t>
+          <t>-5.91%1115</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+6.81%</t>
+          <t>-5.91%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5565</v>
+        <v>1115</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.03%71,000</t>
+          <t>2.11%337,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>71000</v>
+        <v>337000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:44</t>
+          <t>2026-10-29 23:19:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+9.72%1185</t>
+          <t>-6.74%5190</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+9.72%</t>
+          <t>-6.74%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1185</v>
+        <v>5190</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.00%337,000</t>
+          <t>2.08%71,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>337000</v>
+        <v>71000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:45</t>
+          <t>2026-10-29 23:19:54</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2382廣達</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+0.76%330</t>
+          <t>-6.49%7640</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>-6.49%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>330</v>
+        <v>7640</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.98%1,099,000</t>
+          <t>1.94%45,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1099000</v>
+        <v>45000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:45</t>
+          <t>2026-10-29 23:19:54</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>2382廣達</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0%1950</t>
+          <t>-3.64%318</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-3.64%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1950</v>
+        <v>318</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.98%185,105</t>
+          <t>1.91%1,099,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>185105</v>
+        <v>1099000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:45</t>
+          <t>2026-10-29 23:19:54</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+9.96%8170</t>
+          <t>-3.33%1885</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>-3.33%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>8170</v>
+        <v>1885</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.84%45,000</t>
+          <t>1.90%185,105</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.90%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>45000</v>
+        <v>185105</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:45</t>
+          <t>2026-10-29 23:19:54</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+7.99%17295</t>
+          <t>-1.82%16980</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+7.99%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>17295</v>
+        <v>16980</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.79%20,300</t>
+          <t>1.85%20,300</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:45</t>
+          <t>2026-10-29 23:19:54</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>2344華邦電</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+3.59%1300</t>
+          <t>-0.87%170.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+3.59%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1300</v>
+        <v>170.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.73%251,000</t>
+          <t>1.75%1,935,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>251000</v>
+        <v>1935000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:45</t>
+          <t>2026-10-29 23:19:54</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+2.1%194.5</t>
+          <t>-3.85%1250</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>-3.85%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>194.5</v>
+        <v>1250</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.73%1,658,000</t>
+          <t>1.72%251,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1658000</v>
+        <v>251000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:45</t>
+          <t>2026-10-29 23:19:54</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+5.52%172</t>
+          <t>-3.08%188.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+5.52%</t>
+          <t>-3.08%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>172</v>
+        <v>188.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.73%1,935,000</t>
+          <t>1.70%1,658,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1935000</v>
+        <v>1658000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:45</t>
+          <t>2026-10-29 23:19:54</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+1.4%362.5</t>
+          <t>-5.38%343</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+1.4%</t>
+          <t>-5.38%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>362.5</v>
+        <v>343</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.72%877,000</t>
+          <t>1.68%877,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:45</t>
+          <t>2026-10-29 23:19:54</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+3.2%2580</t>
+          <t>-0.19%2575</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+3.2%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2580</v>
+        <v>2575</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.64%119,600</t>
+          <t>1.63%119,600</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:45</t>
+          <t>2026-10-29 23:19:54</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2891中信金</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-1.07%74.2</t>
+          <t>-5.67%4655</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-1.07%</t>
+          <t>-5.67%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>74.2</v>
+        <v>4655</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.61%3,904,000</t>
+          <t>1.59%61,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>3904000</v>
+        <v>61000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:45</t>
+          <t>2026-10-29 23:19:54</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+3.35%4935</t>
+          <t>-9.77%115.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+3.35%</t>
+          <t>-9.77%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4935</v>
+        <v>115.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.60%61,000</t>
+          <t>1.54%2,279,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>61000</v>
+        <v>2279000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:45</t>
+          <t>2026-10-29 23:19:54</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,25 +2090,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>2891中信金</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+4.49%128</t>
+          <t>+1.48%75.3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+4.49%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>128</v>
+        <v>75.3</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.53%2,279,000</t>
+          <t>1.53%3,904,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2117,11 +2117,11 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>2279000</v>
+        <v>3904000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:45</t>
+          <t>2026-10-29 23:19:54</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+4.29%778</t>
+          <t>-4.24%745</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+4.29%</t>
+          <t>-4.24%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>778</v>
+        <v>745</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:45</t>
+          <t>2026-10-29 23:19:54</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+4.32%1810</t>
+          <t>-7.34%959</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+4.32%</t>
+          <t>-7.34%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1810</v>
+        <v>959</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.37%143,336</t>
+          <t>1.45%266,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>143336</v>
+        <v>266000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:45</t>
+          <t>2026-10-29 23:19:54</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,25 +2273,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+9.99%1035</t>
+          <t>-5.8%1705</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+9.99%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1035</v>
+        <v>1705</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.37%266,000</t>
+          <t>1.37%143,336</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2300,11 +2300,11 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>266000</v>
+        <v>143336</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:46</t>
+          <t>2026-10-29 23:19:55</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,25 +2334,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2884玉山金</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-2.22%48.35</t>
+          <t>-5.38%4840</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>-5.38%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>48.35</v>
+        <v>4840</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.32%4,850,622</t>
+          <t>1.32%49,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2361,11 +2361,11 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>4850622</v>
+        <v>49000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:46</t>
+          <t>2026-10-29 23:19:55</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+4.21%544</t>
+          <t>-1.47%536</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+4.21%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:46</t>
+          <t>2026-10-29 23:19:55</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+6.78%5115</t>
+          <t>+1.09%1390</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+6.78%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>5115</v>
+        <v>1390</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.29%49,000</t>
+          <t>1.28%176,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>49000</v>
+        <v>176000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:46</t>
+          <t>2026-10-29 23:19:55</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,25 +2517,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2884玉山金</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+7.42%1375</t>
+          <t>+1.34%49</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+7.42%</t>
+          <t>+1.34%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1375</v>
+        <v>49</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.24%176,000</t>
+          <t>1.24%4,850,622</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2544,11 +2544,11 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>176000</v>
+        <v>4850622</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:46</t>
+          <t>2026-10-29 23:19:55</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+4.09%2035</t>
+          <t>-4.42%1945</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+4.09%</t>
+          <t>-4.42%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2035</v>
+        <v>1945</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:46</t>
+          <t>2026-10-29 23:19:55</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,25 +2644,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+6.37%751</t>
+          <t>+2.13%767</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+6.37%</t>
+          <t>+2.13%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>751</v>
+        <v>767</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.11%286,000</t>
+          <t>1.13%286,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:46</t>
+          <t>2026-10-29 23:19:55</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+6.81%2040</t>
+          <t>+0.49%2050</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+6.81%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.09%104,000</t>
+          <t>1.12%104,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:46</t>
+          <t>2026-10-29 23:19:55</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.93%217</t>
+          <t>-1.38%214</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.93%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1.07%906,000</t>
+          <t>1.04%906,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:46</t>
+          <t>2026-10-29 23:19:55</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+3.13%1815</t>
+          <t>-3.31%1755</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+3.13%</t>
+          <t>-3.31%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1815</v>
+        <v>1755</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.97%100,000</t>
+          <t>0.96%100,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:46</t>
+          <t>2026-10-29 23:19:55</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+4.99%547</t>
+          <t>-0.73%543</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+4.99%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:46</t>
+          <t>2026-10-29 23:19:55</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-4.23%237.5</t>
+          <t>-0.42%236.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-4.23%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>237.5</v>
+        <v>236.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.89%650,000</t>
+          <t>0.81%650,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:46</t>
+          <t>2026-10-29 23:19:55</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,34 +3005,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>5904寶雅*</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.24%71.8</t>
+          <t>-1.42%2425</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-1.42%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>71.8</v>
+        <v>2425</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.68%1,708,500</t>
+          <t>0.70%54,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>1708500</v>
+        <v>54000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:46</t>
+          <t>2026-10-29 23:19:55</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>7751竑騰</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+9.33%2460</t>
+          <t>-2.8%1390</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+9.33%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2460</v>
+        <v>1390</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.67%54,000</t>
+          <t>0.69%91,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>54000</v>
+        <v>91000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:46</t>
+          <t>2026-10-29 23:19:55</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>7751竑騰</t>
+          <t>5904寶雅*</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+7.12%1430</t>
+          <t>+1.39%72.8</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+7.12%</t>
+          <t>+1.39%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1430</v>
+        <v>72.8</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.67%91,000</t>
+          <t>0.65%1,708,500</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.65%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>91000</v>
+        <v>1708500</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:46</t>
+          <t>2026-10-29 23:19:55</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,25 +3188,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3293鈊象</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+0.5%800</t>
+          <t>-2.52%1545</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>-2.52%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>800</v>
+        <v>1545</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.48%110,000</t>
+          <t>0.48%58,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3215,11 +3215,11 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>110000</v>
+        <v>58000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:47</t>
+          <t>2026-10-29 23:19:57</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,38 +3249,38 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>3293鈊象</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+8.19%1585</t>
+          <t>+1%808</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+8.19%</t>
+          <t>+1%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1585</v>
+        <v>808</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.47%58,000</t>
+          <t>0.46%110,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>58000</v>
+        <v>110000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:47</t>
+          <t>2026-10-29 23:19:57</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,25 +3315,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+0.77%781</t>
+          <t>-3.2%756</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>781</v>
+        <v>756</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.40%95,000</t>
+          <t>0.39%95,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:47</t>
+          <t>2026-10-29 23:19:57</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,25 +3376,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+1.81%1405</t>
+          <t>-7.12%1305</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+1.81%</t>
+          <t>-7.12%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1405</v>
+        <v>1305</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.29%38,000</t>
+          <t>0.28%38,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:47</t>
+          <t>2026-10-29 23:19:57</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,25 +3437,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+0.63%398.5</t>
+          <t>-2.63%388</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>-2.63%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>398.5</v>
+        <v>388</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.28%129,000</t>
+          <t>0.27%129,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:47</t>
+          <t>2026-10-29 23:19:57</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+5.57%2655</t>
+          <t>-4.33%2540</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+5.57%</t>
+          <t>-4.33%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>2655</v>
+        <v>2540</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-10-29_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-29_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:57</t>
+          <t>2026-10-29 23:32:46</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:57</t>
+          <t>2026-10-29 23:32:46</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:57</t>
+          <t>2026-10-29 23:32:46</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:57</t>
+          <t>2026-10-29 23:32:46</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:57</t>
+          <t>2026-10-29 23:32:46</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
